--- a/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 5,23</t>
+          <t>-10,43; 4,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,0</t>
+          <t>-4,17; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 14,51</t>
+          <t>-1,22; 14,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 8,89</t>
+          <t>-8,39; 9,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-80,35; 193,17</t>
+          <t>-83,34; 185,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54066536,72</t>
+          <t>-100,0; 50695863,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,9; 205,18</t>
+          <t>-69,17; 188,99</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,3</t>
+          <t>-1,82; 1,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,42</t>
+          <t>0,11; 4,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,21</t>
+          <t>-2,31; 3,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,33</t>
+          <t>-3,31; 2,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,73; 127,7</t>
+          <t>-68,55; 145,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 497,85</t>
+          <t>-3,95; 497,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 85,26</t>
+          <t>-38,34; 85,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 48,38</t>
+          <t>-39,63; 43,68</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,7</t>
+          <t>-4,5; 2,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,87</t>
+          <t>-0,92; 4,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 1,58</t>
+          <t>-6,18; 1,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,37</t>
+          <t>-3,65; 1,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-89,71; 136,65</t>
+          <t>-87,41; 232,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-84,78; 85,81</t>
+          <t>-84,54; 83,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,94; 159,36</t>
+          <t>-89,65; 164,2</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,87</t>
+          <t>-2,13; 0,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,37</t>
+          <t>0,07; 3,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,26</t>
+          <t>-1,83; 2,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,7</t>
+          <t>-2,5; 1,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 50,99</t>
+          <t>-60,02; 51,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 423,77</t>
+          <t>-5,64; 386,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 59,16</t>
+          <t>-31,89; 69,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 36,32</t>
+          <t>-36,98; 32,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 4,83</t>
+          <t>-9,58; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,0</t>
+          <t>-3,1; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 14,16</t>
+          <t>-0,35; 14,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 9,17</t>
+          <t>-8,96; 8,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 185,94</t>
+          <t>-81,85; 177,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50695863,99</t>
+          <t>-100,0; 58577617,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,17; 188,99</t>
+          <t>-74,73; 213,27</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,37</t>
+          <t>-1,82; 1,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,4</t>
+          <t>0,11; 4,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,01</t>
+          <t>-2,04; 3,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,33</t>
+          <t>-3,03; 2,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,55; 145,13</t>
+          <t>-68,99; 145,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 497,66</t>
+          <t>-4,47; 436,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 85,6</t>
+          <t>-34,33; 87,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 43,68</t>
+          <t>-38,67; 50,24</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,0</t>
+          <t>-4,66; 1,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,86</t>
+          <t>-0,9; 5,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,54</t>
+          <t>-6,64; 1,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,43</t>
+          <t>-3,53; 1,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-87,41; 232,19</t>
+          <t>-87,64; 189,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-84,54; 83,33</t>
+          <t>-85,86; 83,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-89,65; 164,2</t>
+          <t>-90,5; 147,36</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,93</t>
+          <t>-2,07; 1,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,22</t>
+          <t>0,19; 3,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,56</t>
+          <t>-1,99; 2,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,57</t>
+          <t>-2,39; 1,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 51,67</t>
+          <t>-60,37; 56,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 386,7</t>
+          <t>2,47; 391,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 69,55</t>
+          <t>-34,43; 66,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 32,65</t>
+          <t>-34,6; 38,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,52%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 5,26</t>
+          <t>-9,92; 5,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,0</t>
+          <t>-4,06; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 14,55</t>
+          <t>-1,12; 14,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 8,55</t>
+          <t>-9,06; 11,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-81,85; 177,02</t>
+          <t>-80,35; 193,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 58577617,73</t>
+          <t>-100,0; 54066536,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,73; 213,27</t>
+          <t>-68,46; 239,5</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,38%</t>
+          <t>-0,77%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,43</t>
+          <t>-1,82; 1,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,33</t>
+          <t>0,04; 4,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,1</t>
+          <t>-2,1; 3,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,48</t>
+          <t>-3,33; 2,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,99; 145,63</t>
+          <t>-69,73; 127,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 436,96</t>
+          <t>-8,3; 497,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 87,97</t>
+          <t>-32,69; 85,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 50,24</t>
+          <t>-38,25; 49,65</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-32,85%</t>
+          <t>-21,61%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 1,84</t>
+          <t>-4,56; 1,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,07</t>
+          <t>-0,79; 4,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,64</t>
+          <t>-6,14; 1,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,47</t>
+          <t>-3,1; 1,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-87,64; 189,8</t>
+          <t>-89,71; 136,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-85,86; 83,88</t>
+          <t>-84,78; 85,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-90,5; 147,36</t>
+          <t>-87,39; 196,42</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,74%</t>
+          <t>-1,79%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,03</t>
+          <t>-2,11; 0,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,32</t>
+          <t>0,19; 3,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,5</t>
+          <t>-1,92; 2,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,77</t>
+          <t>-2,48; 2,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 56,46</t>
+          <t>-59,06; 50,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 391,45</t>
+          <t>3,81; 423,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 66,33</t>
+          <t>-32,91; 59,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,6; 38,94</t>
+          <t>-34,03; 40,28</t>
         </is>
       </c>
     </row>
